--- a/aplicaciones/www/estaticos/datos/descarga/ya7-1-gini.xlsx
+++ b/aplicaciones/www/estaticos/datos/descarga/ya7-1-gini.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28110"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniel/Documents/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -417,9 +417,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADA2738-F688-604C-B3D5-D94E2AC69DC8}">
   <dimension ref="A1:C431"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>99001</v>
       </c>
@@ -438,7 +438,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>99000</v>
       </c>
@@ -446,7 +446,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>97001</v>
       </c>
@@ -454,7 +454,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>97000</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>95001</v>
       </c>
@@ -470,7 +470,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>95000</v>
       </c>
@@ -478,7 +478,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>94001</v>
       </c>
@@ -486,7 +486,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>94000</v>
       </c>
@@ -494,7 +494,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>91001</v>
       </c>
@@ -502,7 +502,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>91000</v>
       </c>
@@ -510,7 +510,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>88000</v>
       </c>
@@ -518,7 +518,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>86001</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>86000</v>
       </c>
@@ -534,7 +534,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>85001</v>
       </c>
@@ -542,7 +542,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>85000</v>
       </c>
@@ -550,7 +550,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>81001</v>
       </c>
@@ -558,7 +558,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>81000</v>
       </c>
@@ -566,7 +566,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>76001</v>
       </c>
@@ -577,7 +577,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>76000</v>
       </c>
@@ -588,7 +588,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>73001</v>
       </c>
@@ -599,7 +599,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>73000</v>
       </c>
@@ -610,7 +610,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>70001</v>
       </c>
@@ -621,7 +621,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>70000</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>68001</v>
       </c>
@@ -643,7 +643,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>68000</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>66001</v>
       </c>
@@ -665,7 +665,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>66000</v>
       </c>
@@ -676,7 +676,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>63001</v>
       </c>
@@ -684,7 +684,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>63000</v>
       </c>
@@ -695,7 +695,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>54001</v>
       </c>
@@ -706,7 +706,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>54000</v>
       </c>
@@ -717,7 +717,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>52001</v>
       </c>
@@ -728,7 +728,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>52000</v>
       </c>
@@ -739,7 +739,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>50001</v>
       </c>
@@ -750,7 +750,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>50000</v>
       </c>
@@ -761,7 +761,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>47001</v>
       </c>
@@ -772,7 +772,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>47000</v>
       </c>
@@ -783,7 +783,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>44001</v>
       </c>
@@ -794,7 +794,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>44000</v>
       </c>
@@ -805,7 +805,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>41001</v>
       </c>
@@ -816,7 +816,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>41000</v>
       </c>
@@ -827,7 +827,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>27001</v>
       </c>
@@ -838,7 +838,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>27000</v>
       </c>
@@ -849,7 +849,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>25000</v>
       </c>
@@ -860,7 +860,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>23001</v>
       </c>
@@ -871,7 +871,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>23000</v>
       </c>
@@ -882,7 +882,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>20001</v>
       </c>
@@ -893,7 +893,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>20000</v>
       </c>
@@ -904,7 +904,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>19001</v>
       </c>
@@ -915,7 +915,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>19000</v>
       </c>
@@ -926,7 +926,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>18001</v>
       </c>
@@ -937,7 +937,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>18000</v>
       </c>
@@ -948,7 +948,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>17001</v>
       </c>
@@ -959,7 +959,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>17000</v>
       </c>
@@ -970,7 +970,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>15001</v>
       </c>
@@ -981,7 +981,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>15000</v>
       </c>
@@ -992,7 +992,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>13001</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>13000</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>11001</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>8001</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>8000</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>5001</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>5000</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>1001</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>1001</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>5000</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>5001</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>8000</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>8001</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>11001</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>13000</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>13001</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>15000</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>15001</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>17000</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>17001</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>18000</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>18001</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>19000</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>19001</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>20000</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>20001</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>23000</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>23001</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>25000</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>27000</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>27001</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3">
       <c r="A89">
         <v>41000</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>41001</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>44000</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>44001</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>47000</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>47001</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3">
       <c r="A95">
         <v>50000</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3">
       <c r="A96">
         <v>50001</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3">
       <c r="A97">
         <v>52000</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>52001</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>54000</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>54001</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>63000</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>63001</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>66000</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3">
       <c r="A104">
         <v>66001</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3">
       <c r="A105">
         <v>68000</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3">
       <c r="A106">
         <v>68001</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3">
       <c r="A107">
         <v>70000</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3">
       <c r="A108">
         <v>70001</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3">
       <c r="A109">
         <v>73000</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3">
       <c r="A110">
         <v>73001</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3">
       <c r="A111">
         <v>76000</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3">
       <c r="A112">
         <v>76001</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3">
       <c r="A113">
         <v>81000</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3">
       <c r="A114">
         <v>81001</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3">
       <c r="A115">
         <v>85000</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3">
       <c r="A116">
         <v>85001</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3">
       <c r="A117">
         <v>86000</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3">
       <c r="A118">
         <v>86001</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3">
       <c r="A119">
         <v>88000</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3">
       <c r="A120">
         <v>91000</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3">
       <c r="A121">
         <v>91001</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3">
       <c r="A122">
         <v>94000</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3">
       <c r="A123">
         <v>94001</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3">
       <c r="A124">
         <v>95000</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3">
       <c r="A125">
         <v>95001</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3">
       <c r="A126">
         <v>97000</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3">
       <c r="A127">
         <v>97001</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3">
       <c r="A128">
         <v>99000</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3">
       <c r="A129">
         <v>99001</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3">
       <c r="A130">
         <v>99001</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3">
       <c r="A131">
         <v>99000</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3">
       <c r="A132">
         <v>97001</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3">
       <c r="A133">
         <v>97000</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3">
       <c r="A134">
         <v>95001</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3">
       <c r="A135">
         <v>95000</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3">
       <c r="A136">
         <v>94001</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3">
       <c r="A137">
         <v>94000</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3">
       <c r="A138">
         <v>91001</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3">
       <c r="A139">
         <v>91000</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3">
       <c r="A140">
         <v>88000</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3">
       <c r="A141">
         <v>86001</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3">
       <c r="A142">
         <v>86000</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3">
       <c r="A143">
         <v>85001</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3">
       <c r="A144">
         <v>85000</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3">
       <c r="A145">
         <v>81001</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3">
       <c r="A146">
         <v>81000</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3">
       <c r="A147">
         <v>76001</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3">
       <c r="A148">
         <v>76000</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3">
       <c r="A149">
         <v>73001</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3">
       <c r="A150">
         <v>73000</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3">
       <c r="A151">
         <v>70001</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3">
       <c r="A152">
         <v>70000</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3">
       <c r="A153">
         <v>68001</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3">
       <c r="A154">
         <v>68000</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3">
       <c r="A155">
         <v>66001</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3">
       <c r="A156">
         <v>66000</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3">
       <c r="A157">
         <v>63001</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3">
       <c r="A158">
         <v>63000</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3">
       <c r="A159">
         <v>54001</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3">
       <c r="A160">
         <v>54000</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3">
       <c r="A161">
         <v>52001</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3">
       <c r="A162">
         <v>52000</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3">
       <c r="A163">
         <v>50001</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3">
       <c r="A164">
         <v>50000</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3">
       <c r="A165">
         <v>47001</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3">
       <c r="A166">
         <v>47000</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3">
       <c r="A167">
         <v>44001</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3">
       <c r="A168">
         <v>44000</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3">
       <c r="A169">
         <v>41001</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3">
       <c r="A170">
         <v>41000</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3">
       <c r="A171">
         <v>27001</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3">
       <c r="A172">
         <v>27000</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3">
       <c r="A173">
         <v>25000</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3">
       <c r="A174">
         <v>23001</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3">
       <c r="A175">
         <v>23000</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3">
       <c r="A176">
         <v>20001</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3">
       <c r="A177">
         <v>20000</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3">
       <c r="A178">
         <v>19001</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3">
       <c r="A179">
         <v>19000</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3">
       <c r="A180">
         <v>18001</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3">
       <c r="A181">
         <v>18000</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3">
       <c r="A182">
         <v>17001</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3">
       <c r="A183">
         <v>17000</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3">
       <c r="A184">
         <v>15001</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3">
       <c r="A185">
         <v>15000</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3">
       <c r="A186">
         <v>13001</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3">
       <c r="A187">
         <v>13000</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3">
       <c r="A188">
         <v>11001</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3">
       <c r="A189">
         <v>8001</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3">
       <c r="A190">
         <v>8000</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3">
       <c r="A191">
         <v>5001</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3">
       <c r="A192">
         <v>5000</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3">
       <c r="A193">
         <v>1001</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3">
       <c r="A194">
         <v>1001</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3">
       <c r="A195">
         <v>5000</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3">
       <c r="A196">
         <v>5001</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3">
       <c r="A197">
         <v>8000</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3">
       <c r="A198">
         <v>8001</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3">
       <c r="A199">
         <v>11001</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3">
       <c r="A200">
         <v>13000</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3">
       <c r="A201">
         <v>13001</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3">
       <c r="A202">
         <v>15000</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3">
       <c r="A203">
         <v>15001</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3">
       <c r="A204">
         <v>17000</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3">
       <c r="A205">
         <v>17001</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3">
       <c r="A206">
         <v>18000</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3">
       <c r="A207">
         <v>18001</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3">
       <c r="A208">
         <v>19000</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3">
       <c r="A209">
         <v>19001</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3">
       <c r="A210">
         <v>20000</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3">
       <c r="A211">
         <v>20001</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3">
       <c r="A212">
         <v>23000</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3">
       <c r="A213">
         <v>23001</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3">
       <c r="A214">
         <v>25000</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3">
       <c r="A215">
         <v>27000</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3">
       <c r="A216">
         <v>27001</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3">
       <c r="A217">
         <v>41000</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3">
       <c r="A218">
         <v>41001</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3">
       <c r="A219">
         <v>44000</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3">
       <c r="A220">
         <v>44001</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3">
       <c r="A221">
         <v>47000</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3">
       <c r="A222">
         <v>47001</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3">
       <c r="A223">
         <v>50000</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3">
       <c r="A224">
         <v>50001</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3">
       <c r="A225">
         <v>52000</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3">
       <c r="A226">
         <v>52001</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3">
       <c r="A227">
         <v>54000</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3">
       <c r="A228">
         <v>54001</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3">
       <c r="A229">
         <v>63000</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3">
       <c r="A230">
         <v>63001</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3">
       <c r="A231">
         <v>66000</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3">
       <c r="A232">
         <v>66001</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3">
       <c r="A233">
         <v>68000</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3">
       <c r="A234">
         <v>68001</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3">
       <c r="A235">
         <v>70000</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3">
       <c r="A236">
         <v>70001</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3">
       <c r="A237">
         <v>73000</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3">
       <c r="A238">
         <v>73001</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3">
       <c r="A239">
         <v>76000</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3">
       <c r="A240">
         <v>76001</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3">
       <c r="A241">
         <v>76001</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3">
       <c r="A242">
         <v>76000</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3">
       <c r="A243">
         <v>81000</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3">
       <c r="A244">
         <v>81001</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3">
       <c r="A245">
         <v>85000</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3">
       <c r="A246">
         <v>85001</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3">
       <c r="A247">
         <v>86000</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3">
       <c r="A248">
         <v>86001</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3">
       <c r="A249">
         <v>88000</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:3">
       <c r="A250">
         <v>91000</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:3">
       <c r="A251">
         <v>91001</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:3">
       <c r="A252">
         <v>73001</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:3">
       <c r="A253">
         <v>73000</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:3">
       <c r="A254">
         <v>70001</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:3">
       <c r="A255">
         <v>70000</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:3">
       <c r="A256">
         <v>68001</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:3">
       <c r="A257">
         <v>68000</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:3">
       <c r="A258">
         <v>66001</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:3">
       <c r="A259">
         <v>66000</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:3">
       <c r="A260">
         <v>63001</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:3">
       <c r="A261">
         <v>63000</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:3">
       <c r="A262">
         <v>54001</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:3">
       <c r="A263">
         <v>54000</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:3">
       <c r="A264">
         <v>52001</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:3">
       <c r="A265">
         <v>52000</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:3">
       <c r="A266">
         <v>50001</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:3">
       <c r="A267">
         <v>50000</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:3">
       <c r="A268">
         <v>47001</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:3">
       <c r="A269">
         <v>47000</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:3">
       <c r="A270">
         <v>44001</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:3">
       <c r="A271">
         <v>44000</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:3">
       <c r="A272">
         <v>41001</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:3">
       <c r="A273">
         <v>41000</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:3">
       <c r="A274">
         <v>27001</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:3">
       <c r="A275">
         <v>27000</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:3">
       <c r="A276">
         <v>25000</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:3">
       <c r="A277">
         <v>23001</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:3">
       <c r="A278">
         <v>23000</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:3">
       <c r="A279">
         <v>20001</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:3">
       <c r="A280">
         <v>20000</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:3">
       <c r="A281">
         <v>19001</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:3">
       <c r="A282">
         <v>19000</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:3">
       <c r="A283">
         <v>18001</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:3">
       <c r="A284">
         <v>18000</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:3">
       <c r="A285">
         <v>17001</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:3">
       <c r="A286">
         <v>17000</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:3">
       <c r="A287">
         <v>15001</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:3">
       <c r="A288">
         <v>15000</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:3">
       <c r="A289">
         <v>13001</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:3">
       <c r="A290">
         <v>13000</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:3">
       <c r="A291">
         <v>11001</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:3">
       <c r="A292">
         <v>8001</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:3">
       <c r="A293">
         <v>8000</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:3">
       <c r="A294">
         <v>5001</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:3">
       <c r="A295">
         <v>5000</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:3">
       <c r="A296">
         <v>1001</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:3">
       <c r="A297">
         <v>94000</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3">
       <c r="A298">
         <v>94001</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3">
       <c r="A299">
         <v>95000</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3">
       <c r="A300">
         <v>95001</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3">
       <c r="A301">
         <v>97000</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3">
       <c r="A302">
         <v>97001</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3">
       <c r="A303">
         <v>99000</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3">
       <c r="A304">
         <v>99001</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:3">
       <c r="A305">
         <v>99001</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:3">
       <c r="A306">
         <v>99000</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:3">
       <c r="A307">
         <v>97001</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:3">
       <c r="A308">
         <v>97000</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:3">
       <c r="A309">
         <v>95001</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:3">
       <c r="A310">
         <v>95000</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:3">
       <c r="A311">
         <v>94001</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:3">
       <c r="A312">
         <v>94000</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:3">
       <c r="A313">
         <v>1001</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:3">
       <c r="A314">
         <v>5000</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:3">
       <c r="A315">
         <v>5001</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:3">
       <c r="A316">
         <v>8000</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:3">
       <c r="A317">
         <v>8001</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:3">
       <c r="A318">
         <v>11001</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:3">
       <c r="A319">
         <v>13000</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:3">
       <c r="A320">
         <v>13001</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:3">
       <c r="A321">
         <v>15000</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:3">
       <c r="A322">
         <v>15001</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:3">
       <c r="A323">
         <v>17000</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3">
       <c r="A324">
         <v>17001</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3">
       <c r="A325">
         <v>18000</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3">
       <c r="A326">
         <v>18001</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3">
       <c r="A327">
         <v>19000</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3">
       <c r="A328">
         <v>19001</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:3">
       <c r="A329">
         <v>20000</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3">
       <c r="A330">
         <v>20001</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:3">
       <c r="A331">
         <v>23000</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:3">
       <c r="A332">
         <v>23001</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:3">
       <c r="A333">
         <v>25000</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:3">
       <c r="A334">
         <v>27000</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:3">
       <c r="A335">
         <v>27001</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:3">
       <c r="A336">
         <v>41000</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:3">
       <c r="A337">
         <v>41001</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:3">
       <c r="A338">
         <v>44000</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:3">
       <c r="A339">
         <v>44001</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:3">
       <c r="A340">
         <v>47000</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:3">
       <c r="A341">
         <v>47001</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:3">
       <c r="A342">
         <v>50000</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:3">
       <c r="A343">
         <v>50001</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:3">
       <c r="A344">
         <v>52000</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:3">
       <c r="A345">
         <v>52001</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:3">
       <c r="A346">
         <v>54000</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:3">
       <c r="A347">
         <v>54001</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:3">
       <c r="A348">
         <v>63000</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:3">
       <c r="A349">
         <v>63001</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:3">
       <c r="A350">
         <v>66000</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:3">
       <c r="A351">
         <v>66001</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:3">
       <c r="A352">
         <v>68000</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3">
       <c r="A353">
         <v>68001</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:3">
       <c r="A354">
         <v>70000</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:3">
       <c r="A355">
         <v>70001</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:3">
       <c r="A356">
         <v>73000</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:3">
       <c r="A357">
         <v>73001</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:3">
       <c r="A358">
         <v>91001</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:3">
       <c r="A359">
         <v>91000</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:3">
       <c r="A360">
         <v>88000</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:3">
       <c r="A361">
         <v>86001</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:3">
       <c r="A362">
         <v>86000</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:3">
       <c r="A363">
         <v>85001</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:3">
       <c r="A364">
         <v>85000</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:3">
       <c r="A365">
         <v>81001</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:3">
       <c r="A366">
         <v>81000</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:3">
       <c r="A367">
         <v>76000</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:3">
       <c r="A368">
         <v>76001</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:3">
       <c r="A369">
         <v>76001</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:3">
       <c r="A370">
         <v>76000</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:3">
       <c r="A371">
         <v>81000</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:3">
       <c r="A372">
         <v>81001</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:3">
       <c r="A373">
         <v>85000</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:3">
       <c r="A374">
         <v>85001</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:3">
       <c r="A375">
         <v>86000</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:3">
       <c r="A376">
         <v>86001</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:3">
       <c r="A377">
         <v>88000</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:3">
       <c r="A378">
         <v>91000</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:3">
       <c r="A379">
         <v>91001</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:3">
       <c r="A380">
         <v>73001</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:3">
       <c r="A381">
         <v>73000</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:3">
       <c r="A382">
         <v>70001</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:3">
       <c r="A383">
         <v>70000</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:3">
       <c r="A384">
         <v>68001</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:3">
       <c r="A385">
         <v>68000</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:3">
       <c r="A386">
         <v>66001</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:3">
       <c r="A387">
         <v>66000</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3">
       <c r="A388">
         <v>63001</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:3">
       <c r="A389">
         <v>63000</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:3">
       <c r="A390">
         <v>54001</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:3">
       <c r="A391">
         <v>54000</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:3">
       <c r="A392">
         <v>52001</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:3">
       <c r="A393">
         <v>52000</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:3">
       <c r="A394">
         <v>50001</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3">
       <c r="A395">
         <v>50000</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3">
       <c r="A396">
         <v>47001</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3">
       <c r="A397">
         <v>47000</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3">
       <c r="A398">
         <v>44001</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3">
       <c r="A399">
         <v>44000</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3">
       <c r="A400">
         <v>41001</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:3">
       <c r="A401">
         <v>41000</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:3">
       <c r="A402">
         <v>27001</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:3">
       <c r="A403">
         <v>27000</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:3">
       <c r="A404">
         <v>25000</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:3">
       <c r="A405">
         <v>23001</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:3">
       <c r="A406">
         <v>23000</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:3">
       <c r="A407">
         <v>20001</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:3">
       <c r="A408">
         <v>20000</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:3">
       <c r="A409">
         <v>19001</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:3">
       <c r="A410">
         <v>19000</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:3">
       <c r="A411">
         <v>18001</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:3">
       <c r="A412">
         <v>18000</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:3">
       <c r="A413">
         <v>17001</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3">
       <c r="A414">
         <v>17000</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:3">
       <c r="A415">
         <v>15001</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:3">
       <c r="A416">
         <v>15000</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:3">
       <c r="A417">
         <v>13001</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:3">
       <c r="A418">
         <v>13000</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:3">
       <c r="A419">
         <v>8001</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3">
       <c r="A420">
         <v>8000</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:3">
       <c r="A421">
         <v>5001</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:3">
       <c r="A422">
         <v>5000</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:3">
       <c r="A423">
         <v>1001</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:3">
       <c r="A424">
         <v>94000</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:3">
       <c r="A425">
         <v>94001</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:3">
       <c r="A426">
         <v>95000</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:3">
       <c r="A427">
         <v>95001</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:3">
       <c r="A428">
         <v>97000</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:3">
       <c r="A429">
         <v>97001</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:3">
       <c r="A430">
         <v>99000</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:3">
       <c r="A431">
         <v>99001</v>
       </c>
